--- a/competencia01/ResultadoLicencas.xlsx
+++ b/competencia01/ResultadoLicencas.xlsx
@@ -445,7 +445,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Total Usage</t>
+          <t>End Time</t>
         </is>
       </c>
     </row>
